--- a/Project/outputs/tables/table_lstm_metrics_h10.xlsx
+++ b/Project/outputs/tables/table_lstm_metrics_h10.xlsx
@@ -482,19 +482,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.008573741652071476</v>
+        <v>0.008591659367084503</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05118132382631302</v>
+        <v>0.05075019225478172</v>
       </c>
       <c r="D2" t="n">
-        <v>0.09259450119781129</v>
+        <v>0.09269120436742907</v>
       </c>
       <c r="E2" t="n">
-        <v>32.80796051025391</v>
+        <v>31.59088706970215</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4703632887189292</v>
+        <v>0.4823747680890538</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -513,23 +513,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STOXX600</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003981978632509708</v>
+        <v>0.004529793281108141</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0382947064936161</v>
+        <v>0.043695367872715</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06310292095069536</v>
+        <v>0.06730373898312145</v>
       </c>
       <c r="E3" t="n">
-        <v>27.14337158203125</v>
+        <v>26.24831581115723</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4722753346080306</v>
+        <v>0.4916512059369202</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -548,23 +548,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FTSE100</t>
+          <t>CAC40</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004092910327017307</v>
+        <v>0.005214436911046505</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03938199952244759</v>
+        <v>0.05139420926570892</v>
       </c>
       <c r="D4" t="n">
-        <v>0.06397585737617986</v>
+        <v>0.07221105809394088</v>
       </c>
       <c r="E4" t="n">
-        <v>23.25620651245117</v>
+        <v>34.86379623413086</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5239005736137667</v>
+        <v>0.4749536178107607</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -583,23 +583,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>FTSE100</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.004750317428261042</v>
+        <v>0.003503192681819201</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04741770774126053</v>
+        <v>0.03753619641065598</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06892254658862397</v>
+        <v>0.05918777476657828</v>
       </c>
       <c r="E5" t="n">
-        <v>30.84665298461914</v>
+        <v>23.47787094116211</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4837476099426386</v>
+        <v>0.5102040816326531</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.00174824264831841</v>
+        <v>0.002279963809996843</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03134647384285927</v>
+        <v>0.03836388140916824</v>
       </c>
       <c r="D6" t="n">
-        <v>0.04181199168083733</v>
+        <v>0.04774896658564291</v>
       </c>
       <c r="E6" t="n">
-        <v>17.93313407897949</v>
+        <v>23.87772178649902</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5372848948374761</v>
+        <v>0.5064935064935064</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -653,23 +653,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HangSeng</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002449247753247619</v>
+        <v>0.002814691513776779</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03792421147227287</v>
+        <v>0.03868921473622322</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0494898752599723</v>
+        <v>0.05305366635565142</v>
       </c>
       <c r="E7" t="n">
-        <v>19.31720542907715</v>
+        <v>22.74507522583008</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4780114722753346</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -688,23 +688,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MSCI_EM</t>
+          <t>HangSeng</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00914955697953701</v>
+        <v>0.003303459845483303</v>
       </c>
       <c r="C8" t="n">
-        <v>0.06745776534080505</v>
+        <v>0.04105141386389732</v>
       </c>
       <c r="D8" t="n">
-        <v>0.09565331661545777</v>
+        <v>0.0574757326659113</v>
       </c>
       <c r="E8" t="n">
-        <v>34.73136901855469</v>
+        <v>21.1150074005127</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4435946462715105</v>
+        <v>0.5120593692022264</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -723,23 +723,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CSI300</t>
+          <t>SSE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00355875538662076</v>
+        <v>0.003377366112545133</v>
       </c>
       <c r="C9" t="n">
-        <v>0.04199963435530663</v>
+        <v>0.04744585603475571</v>
       </c>
       <c r="D9" t="n">
-        <v>0.05965530476513183</v>
+        <v>0.05811511087957359</v>
       </c>
       <c r="E9" t="n">
-        <v>22.55134963989258</v>
+        <v>33.52138519287109</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4818355640535373</v>
+        <v>0.4712430426716141</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.004788093850947917</v>
+        <v>0.004201820440357551</v>
       </c>
       <c r="C10" t="n">
-        <v>0.04437547782436013</v>
+        <v>0.04361579148098826</v>
       </c>
       <c r="D10" t="n">
-        <v>0.06690078930433871</v>
+        <v>0.06347340658723111</v>
       </c>
       <c r="E10" t="n">
-        <v>26.07340621948242</v>
+        <v>27.18000793457031</v>
       </c>
       <c r="F10" t="n">
-        <v>0.486376673040153</v>
+        <v>0.4879406307977736</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -797,19 +797,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.002148728584870696</v>
+        <v>0.003609571373090148</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0278723631054163</v>
+        <v>0.03947973251342773</v>
       </c>
       <c r="D11" t="n">
-        <v>0.04635438042807493</v>
+        <v>0.06007970849704705</v>
       </c>
       <c r="E11" t="n">
-        <v>17.79641723632812</v>
+        <v>21.33347320556641</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5195154777927322</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -828,23 +828,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STOXX600</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.001546726445667446</v>
+        <v>0.001805789885111153</v>
       </c>
       <c r="C12" t="n">
-        <v>0.02545002289116383</v>
+        <v>0.03116011992096901</v>
       </c>
       <c r="D12" t="n">
-        <v>0.03932844321438932</v>
+        <v>0.04249458653888932</v>
       </c>
       <c r="E12" t="n">
-        <v>21.38986206054688</v>
+        <v>21.90238952636719</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4724091520861373</v>
+        <v>0.4894179894179894</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -863,23 +863,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FTSE100</t>
+          <t>CAC40</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.001873024739325047</v>
+        <v>0.00169102568179369</v>
       </c>
       <c r="C13" t="n">
-        <v>0.03019956685602665</v>
+        <v>0.03061183169484138</v>
       </c>
       <c r="D13" t="n">
-        <v>0.04327845583341724</v>
+        <v>0.041122082653894</v>
       </c>
       <c r="E13" t="n">
-        <v>30.6751880645752</v>
+        <v>23.60537910461426</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4831763122476447</v>
+        <v>0.5198412698412699</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -898,23 +898,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>FTSE100</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.002285472583025694</v>
+        <v>0.001556473318487406</v>
       </c>
       <c r="C14" t="n">
-        <v>0.03714250400662422</v>
+        <v>0.02737730927765369</v>
       </c>
       <c r="D14" t="n">
-        <v>0.04780661651932391</v>
+        <v>0.03945216494043648</v>
       </c>
       <c r="E14" t="n">
-        <v>28.34440994262695</v>
+        <v>27.56132507324219</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5114401076716016</v>
+        <v>0.5158730158730159</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -937,19 +937,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.006848832126706839</v>
+        <v>0.007769796531647444</v>
       </c>
       <c r="C15" t="n">
-        <v>0.04214682057499886</v>
+        <v>0.05697488784790039</v>
       </c>
       <c r="D15" t="n">
-        <v>0.08275767110490023</v>
+        <v>0.08814644934225907</v>
       </c>
       <c r="E15" t="n">
-        <v>19.44215965270996</v>
+        <v>28.4244499206543</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5047106325706595</v>
+        <v>0.4894179894179894</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -968,23 +968,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HangSeng</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.004770964384078979</v>
+        <v>0.003434707876294851</v>
       </c>
       <c r="C16" t="n">
-        <v>0.04071133583784103</v>
+        <v>0.03984003514051437</v>
       </c>
       <c r="D16" t="n">
-        <v>0.06907216794106712</v>
+        <v>0.05860638084965537</v>
       </c>
       <c r="E16" t="n">
-        <v>15.73640251159668</v>
+        <v>22.7092399597168</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5423956931359354</v>
+        <v>0.5198412698412699</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1003,23 +1003,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MSCI_EM</t>
+          <t>HangSeng</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.005806644912809134</v>
+        <v>0.005583611316978931</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05890676006674767</v>
+        <v>0.04903633147478104</v>
       </c>
       <c r="D17" t="n">
-        <v>0.07620134456037593</v>
+        <v>0.07472356600818066</v>
       </c>
       <c r="E17" t="n">
-        <v>38.10725784301758</v>
+        <v>19.08786964416504</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4643337819650067</v>
+        <v>0.5370370370370371</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1038,23 +1038,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CSI300</t>
+          <t>SSE</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.003236277727410197</v>
+        <v>0.004258234985172749</v>
       </c>
       <c r="C18" t="n">
-        <v>0.03980833292007446</v>
+        <v>0.05389323830604553</v>
       </c>
       <c r="D18" t="n">
-        <v>0.05688829165487568</v>
+        <v>0.06525515293961656</v>
       </c>
       <c r="E18" t="n">
-        <v>28.98091125488281</v>
+        <v>45.62860870361328</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4751009421265142</v>
+        <v>0.4682539682539683</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1077,19 +1077,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.003564583937986754</v>
+        <v>0.003713651371072046</v>
       </c>
       <c r="C19" t="n">
-        <v>0.03777971328236163</v>
+        <v>0.04104668577201664</v>
       </c>
       <c r="D19" t="n">
-        <v>0.05771092140705305</v>
+        <v>0.05873501147124732</v>
       </c>
       <c r="E19" t="n">
-        <v>25.05907440185547</v>
+        <v>26.28159141540527</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4966352624495289</v>
+        <v>0.5079365079365079</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
